--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,73 +553,73 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>12.9926</v>
+        <v>15.1576</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3192</v>
+        <v>9.7182</v>
       </c>
       <c r="F2" t="n">
-        <v>7.6734</v>
+        <v>5.4392</v>
       </c>
       <c r="G2" t="n">
-        <v>6.8054</v>
+        <v>2.3372</v>
       </c>
       <c r="H2" t="n">
-        <v>7.1402</v>
+        <v>4.591200000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3348</v>
+        <v>-2.2538</v>
       </c>
       <c r="J2" t="n">
-        <v>7.413399999999999</v>
+        <v>6.1673</v>
       </c>
       <c r="K2" t="n">
-        <v>7.648400000000001</v>
+        <v>6.5983</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.235</v>
+        <v>-0.4308999999999998</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6082000000000003</v>
+        <v>-3.8302</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5081</v>
+        <v>-2.007</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0998</v>
+        <v>-1.8231</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3398</v>
+        <v>7.7994</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.8747</v>
+        <v>-1.9498</v>
       </c>
       <c r="R2" t="n">
-        <v>7.2146</v>
+        <v>9.7493</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4073</v>
+        <v>0.1406999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2168</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6242</v>
+        <v>0.9658</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4401</v>
+        <v>4.8802</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9972</v>
+        <v>6.3259</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5572</v>
+        <v>-1.4457</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -631,67 +631,67 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>12.7275</v>
+        <v>12.9926</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2882</v>
+        <v>5.3192</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4392</v>
+        <v>7.6734</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.09289999999999998</v>
+        <v>6.8054</v>
       </c>
       <c r="H3" t="n">
-        <v>4.591200000000001</v>
+        <v>7.1402</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.684</v>
+        <v>-0.3348</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7373</v>
+        <v>7.413399999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>6.5983</v>
+        <v>7.648400000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.860999999999999</v>
+        <v>-0.235</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.8302</v>
+        <v>-0.6082000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.007</v>
+        <v>-0.5081</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8231</v>
+        <v>-0.0998</v>
       </c>
       <c r="P3" t="n">
-        <v>7.7994</v>
+        <v>2.3398</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9498</v>
+        <v>-4.8747</v>
       </c>
       <c r="R3" t="n">
-        <v>9.7493</v>
+        <v>7.2146</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1406999999999999</v>
+        <v>1.4073</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.2168</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9658</v>
+        <v>1.6242</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8802</v>
+        <v>2.4401</v>
       </c>
       <c r="W3" t="n">
-        <v>6.3259</v>
+        <v>2.9972</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4457</v>
+        <v>-0.5572</v>
       </c>
     </row>
     <row r="4">
@@ -931,7 +931,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -940,76 +940,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.43</v>
+        <v>1.1909</v>
       </c>
       <c r="E7" t="n">
-        <v>2.43</v>
+        <v>2.8262</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1.6354</v>
       </c>
       <c r="G7" t="n">
-        <v>2.43</v>
+        <v>-2.0104</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.4440999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>2.43</v>
+        <v>-2.4545</v>
       </c>
       <c r="J7" t="n">
-        <v>2.43</v>
+        <v>0.9849</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.3703</v>
       </c>
       <c r="L7" t="n">
-        <v>2.43</v>
+        <v>-1.3855</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-2.9952</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.9261</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.069</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9750000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.9248</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.6511</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.4788</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.1722</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.8775</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.2703</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.3928</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1021,73 +1021,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1909</v>
+        <v>0.4093999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8262</v>
+        <v>-0.07430000000000003</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6354</v>
+        <v>0.4837999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0104</v>
+        <v>1.9082</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4440999999999999</v>
+        <v>1.3997</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4545</v>
+        <v>0.5085999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9849</v>
+        <v>4.3968</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3703</v>
+        <v>2.5832</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3855</v>
+        <v>1.8137</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9952</v>
+        <v>-2.4886</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9261</v>
+        <v>-1.1835</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.069</v>
+        <v>-1.305</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9750000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9499</v>
+        <v>-6.8246</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9248</v>
+        <v>7.2145</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6511</v>
+        <v>-0.2842</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4788</v>
+        <v>-0.591</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1722</v>
+        <v>0.3067</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8775</v>
+        <v>-1.6046</v>
       </c>
       <c r="W8" t="n">
-        <v>4.2703</v>
+        <v>2.9444</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3928</v>
+        <v>-4.5488</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1096,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4093999999999998</v>
+        <v>-1.5438</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07430000000000003</v>
+        <v>-0.7956</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4837999999999999</v>
+        <v>-0.7482</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9082</v>
+        <v>0.3394</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3997</v>
+        <v>0.2033</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5085999999999999</v>
+        <v>0.1361</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3968</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5832</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8137</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4886</v>
+        <v>0.3394</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1835</v>
+        <v>0.2033</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.305</v>
+        <v>0.1361</v>
       </c>
       <c r="P9" t="n">
-        <v>0.39</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.8246</v>
+        <v>-0.9749</v>
       </c>
       <c r="R9" t="n">
-        <v>7.2145</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2842</v>
+        <v>0.3118</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.591</v>
+        <v>0.1793</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3067</v>
+        <v>0.1325</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6046</v>
+        <v>-1.2201</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9444</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.5488</v>
+        <v>-1.2201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1174,76 +1174,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5438</v>
+        <v>-6.8068</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7956</v>
+        <v>-3.2351</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7482</v>
+        <v>-3.5717</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3394</v>
+        <v>-2.0491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2033</v>
+        <v>-1.3366</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1361</v>
+        <v>-0.7124999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.5578000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.6389</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3394</v>
+        <v>-1.4913</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2033</v>
+        <v>-0.6978000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1361</v>
+        <v>-0.7935</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9749</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9749</v>
+        <v>-2.9247</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5599</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3118</v>
+        <v>-0.3955</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1793</v>
+        <v>0.2475000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1325</v>
+        <v>-0.6431</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2201</v>
+        <v>-2.9973</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2201</v>
+        <v>-2.9973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,73 +1255,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8068</v>
+        <v>-8.616400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2351</v>
+        <v>-6.962899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5717</v>
+        <v>-1.6534</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0491</v>
+        <v>-7.8258</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3366</v>
+        <v>-1.9794</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7124999999999999</v>
+        <v>-5.846299999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5578000000000001</v>
+        <v>-6.2839</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6389</v>
+        <v>-1.7624</v>
       </c>
       <c r="L11" t="n">
-        <v>0.081</v>
+        <v>-4.5215</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4913</v>
+        <v>-1.5419</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6978000000000001</v>
+        <v>-0.217</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7935</v>
+        <v>-1.3248</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3649</v>
+        <v>3.3147</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9247</v>
+        <v>-0.9749</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5599</v>
+        <v>4.2897</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3955</v>
+        <v>0.4963</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2475000000000001</v>
+        <v>0.01739999999999995</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6431</v>
+        <v>0.479</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.9973</v>
+        <v>-4.6017</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9973</v>
+        <v>-4.8803</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.616400000000001</v>
+        <v>-12.2268</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.962899999999999</v>
+        <v>-8.681900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6534</v>
+        <v>-3.545</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.8258</v>
+        <v>-2.4603</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9794</v>
+        <v>-2.657</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.846299999999999</v>
+        <v>0.1968</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.2839</v>
+        <v>0.714</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7624</v>
+        <v>-0.3795000000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.5215</v>
+        <v>1.0935</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5419</v>
+        <v>-3.1743</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.217</v>
+        <v>-2.2776</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3248</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3147</v>
+        <v>-3.3148</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9749</v>
+        <v>-8.7743</v>
       </c>
       <c r="R12" t="n">
-        <v>4.2897</v>
+        <v>5.4596</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4963</v>
+        <v>-1.6774</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01739999999999995</v>
+        <v>-1.1787</v>
       </c>
       <c r="U12" t="n">
-        <v>0.479</v>
+        <v>-0.4988</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.6017</v>
+        <v>-4.7745</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2786</v>
+        <v>0.5571</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.8803</v>
+        <v>-5.3316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,73 +1411,73 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.2268</v>
+        <v>-15.1162</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.681900000000001</v>
+        <v>-13.6452</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.545</v>
+        <v>-1.4709</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4603</v>
+        <v>-9.285699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.657</v>
+        <v>-1.6111</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1968</v>
+        <v>-7.6746</v>
       </c>
       <c r="J13" t="n">
-        <v>0.714</v>
+        <v>-4.7011</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3795000000000002</v>
+        <v>-0.6256</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0935</v>
+        <v>-4.0756</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1743</v>
+        <v>-4.5844</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2776</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-3.599</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.3148</v>
+        <v>-3.5097</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.7743</v>
+        <v>-10.7243</v>
       </c>
       <c r="R13" t="n">
-        <v>5.4596</v>
+        <v>7.2145</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6774</v>
+        <v>-1.8166</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1787</v>
+        <v>-1.2701</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4988</v>
+        <v>-0.5465</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.7745</v>
+        <v>-0.5043</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5571</v>
+        <v>3.0502</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.3316</v>
+        <v>-3.5544</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,144 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.1162</v>
+        <v>-0.4094000000000104</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.6452</v>
+        <v>-7.361999999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4709</v>
+        <v>6.952499999999997</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.285699999999999</v>
+        <v>-8.360400000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6111</v>
+        <v>16.0398</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.6746</v>
+        <v>-24.3996</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.7011</v>
+        <v>19.6512</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6256</v>
+        <v>31.6482</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.0756</v>
+        <v>-11.9972</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.5844</v>
+        <v>-28.0115</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-15.6081</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.599</v>
+        <v>-12.4023</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.5097</v>
+        <v>6.824399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.7243</v>
+        <v>-60.4456</v>
       </c>
       <c r="R14" t="n">
-        <v>7.2145</v>
+        <v>67.27029999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8166</v>
+        <v>0.4779</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2701</v>
+        <v>-3.5285</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5465</v>
+        <v>4.006400000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5043</v>
+        <v>0.6484000000000039</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0502</v>
+        <v>36.96149999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.5544</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JAEN PARAISO INTERIOR FS</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.4095000000000066</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-7.361999999999998</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.952499999999997</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-8.360500000000002</v>
-      </c>
-      <c r="H15" t="n">
-        <v>16.0398</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-24.39980000000001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19.6512</v>
-      </c>
-      <c r="K15" t="n">
-        <v>31.6482</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-11.9973</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-28.0115</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-15.6081</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-12.4023</v>
-      </c>
-      <c r="P15" t="n">
-        <v>6.824399999999999</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-60.4456</v>
-      </c>
-      <c r="R15" t="n">
-        <v>67.27029999999999</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.4779</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-3.5285</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.006400000000001</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.6484000000000039</v>
-      </c>
-      <c r="W15" t="n">
-        <v>36.96149999999999</v>
-      </c>
-      <c r="X15" t="n">
         <v>-36.3128</v>
       </c>
     </row>
